--- a/Truths-description.xlsx
+++ b/Truths-description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matteoperini/Library/CloudStorage/Box-Box/Matteo Perini/13_NA-returns/Model/NA_SEIR-EAKF-flights/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matteoperini/Library/CloudStorage/Box-Box/Matteo Perini/13_NA-returns/Model/NA_SEIR-EAKF_forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B27D963-3B5A-D94D-A8B4-50AB6D32F8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C631E7F3-1319-EA4D-A77D-42D137E37FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="680" windowWidth="25820" windowHeight="18180" xr2:uid="{DA942B41-D09C-4741-975D-803349827F2C}"/>
+    <workbookView xWindow="4680" yWindow="680" windowWidth="25820" windowHeight="18180" xr2:uid="{DA942B41-D09C-4741-975D-803349827F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="96">
   <si>
     <t>beta</t>
   </si>
@@ -324,19 +324,7 @@
     <t>tr00_real</t>
   </si>
   <si>
-    <t>t999</t>
-  </si>
-  <si>
-    <t>t999_me_NY</t>
-  </si>
-  <si>
-    <t>Patch</t>
-  </si>
-  <si>
     <t>Flight</t>
-  </si>
-  <si>
-    <t>No Flight</t>
   </si>
 </sst>
 </file>
@@ -764,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D76F6C-B8F9-3044-BD3D-2174C4F373AB}">
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:R999"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" bestFit="1" customWidth="1"/>
@@ -797,7 +785,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -1981,30 +1969,14 @@
       <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="1">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F38" s="1">
-        <v>75</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2340,9 +2312,6 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2407,6 +2376,9 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -20262,25 +20234,6 @@
       <c r="P999" s="1"/>
       <c r="Q999" s="1"/>
     </row>
-    <row r="1000" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="1"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
-      <c r="I1000" s="1"/>
-      <c r="J1000" s="1"/>
-      <c r="K1000" s="1"/>
-      <c r="L1000" s="1"/>
-      <c r="M1000" s="1"/>
-      <c r="N1000" s="1"/>
-      <c r="O1000" s="1"/>
-      <c r="P1000" s="1"/>
-      <c r="Q1000" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
